--- a/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 03/01. Báo giá bảo hành/BG_DLMinhKhang_210326.xlsx
+++ b/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 03/01. Báo giá bảo hành/BG_DLMinhKhang_210326.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\4. Workspace\1. Bộ phận bảo hành\1. Thực hiện sửa chữa bảo hành\Năm 2026\Tháng 03\01. Báo giá bảo hành\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{425A3DD3-BDA9-45A0-8B29-14668C8B834E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17FB296C-BBD2-43FE-A6CF-5A61D95557C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -426,13 +426,16 @@
     <xf numFmtId="49" fontId="6" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -516,16 +519,13 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -909,97 +909,97 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="22"/>
-      <c r="B1" s="23"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="32" t="s">
+      <c r="A1" s="23"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33"/>
-      <c r="I1" s="33"/>
-      <c r="J1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="35"/>
     </row>
     <row r="2" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="25"/>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="29" t="s">
+      <c r="A2" s="26"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30"/>
-      <c r="I2" s="30"/>
-      <c r="J2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="32"/>
     </row>
     <row r="3" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="25"/>
-      <c r="B3" s="26"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="35" t="s">
+      <c r="A3" s="26"/>
+      <c r="B3" s="27"/>
+      <c r="C3" s="27"/>
+      <c r="D3" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="36"/>
-      <c r="F3" s="36"/>
-      <c r="G3" s="36"/>
-      <c r="H3" s="36"/>
-      <c r="I3" s="36"/>
-      <c r="J3" s="37"/>
+      <c r="E3" s="37"/>
+      <c r="F3" s="37"/>
+      <c r="G3" s="37"/>
+      <c r="H3" s="37"/>
+      <c r="I3" s="37"/>
+      <c r="J3" s="38"/>
     </row>
     <row r="4" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="27"/>
-      <c r="B4" s="28"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="38" t="s">
+      <c r="A4" s="28"/>
+      <c r="B4" s="29"/>
+      <c r="C4" s="29"/>
+      <c r="D4" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="39"/>
-      <c r="F4" s="39"/>
-      <c r="G4" s="39"/>
-      <c r="H4" s="39"/>
-      <c r="I4" s="39"/>
-      <c r="J4" s="40"/>
+      <c r="E4" s="40"/>
+      <c r="F4" s="40"/>
+      <c r="G4" s="40"/>
+      <c r="H4" s="40"/>
+      <c r="I4" s="40"/>
+      <c r="J4" s="41"/>
     </row>
     <row r="5" spans="1:27" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="45" t="s">
+      <c r="A5" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="46"/>
-      <c r="C5" s="46"/>
-      <c r="D5" s="46"/>
-      <c r="E5" s="46"/>
-      <c r="F5" s="46"/>
-      <c r="G5" s="46"/>
-      <c r="H5" s="46"/>
-      <c r="I5" s="46"/>
-      <c r="J5" s="47"/>
+      <c r="B5" s="47"/>
+      <c r="C5" s="47"/>
+      <c r="D5" s="47"/>
+      <c r="E5" s="47"/>
+      <c r="F5" s="47"/>
+      <c r="G5" s="47"/>
+      <c r="H5" s="47"/>
+      <c r="I5" s="47"/>
+      <c r="J5" s="48"/>
     </row>
     <row r="6" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="41" t="s">
+      <c r="A6" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="B6" s="41"/>
-      <c r="C6" s="41"/>
+      <c r="B6" s="42"/>
+      <c r="C6" s="42"/>
       <c r="D6" s="12"/>
       <c r="E6" s="12"/>
       <c r="F6" s="12"/>
       <c r="G6" s="12"/>
       <c r="H6" s="12"/>
       <c r="I6" s="12"/>
-      <c r="J6" s="48" t="s">
+      <c r="J6" s="18" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="41" t="s">
+      <c r="A7" s="42" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="41"/>
-      <c r="C7" s="41"/>
+      <c r="B7" s="42"/>
+      <c r="C7" s="42"/>
       <c r="D7" s="9"/>
       <c r="E7" s="9"/>
       <c r="F7" s="9" t="s">
@@ -1011,11 +1011,11 @@
       <c r="J7" s="9"/>
     </row>
     <row r="8" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="41" t="s">
+      <c r="A8" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="41"/>
-      <c r="C8" s="41"/>
+      <c r="B8" s="42"/>
+      <c r="C8" s="42"/>
       <c r="D8" s="9"/>
       <c r="E8" s="9"/>
       <c r="F8" s="9"/>
@@ -1026,11 +1026,11 @@
       <c r="AA8" s="2"/>
     </row>
     <row r="9" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="42" t="s">
+      <c r="A9" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="42"/>
-      <c r="C9" s="42"/>
+      <c r="B9" s="43"/>
+      <c r="C9" s="43"/>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="F9" s="9"/>
@@ -1041,34 +1041,34 @@
       <c r="AA9" s="2"/>
     </row>
     <row r="10" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="49" t="s">
+      <c r="A10" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B10" s="49" t="s">
+      <c r="B10" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="49" t="s">
+      <c r="C10" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="49" t="s">
+      <c r="D10" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="E10" s="49" t="s">
+      <c r="E10" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="F10" s="50" t="s">
+      <c r="F10" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="G10" s="49" t="s">
+      <c r="G10" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="H10" s="49" t="s">
+      <c r="H10" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="I10" s="49" t="s">
+      <c r="I10" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="J10" s="49" t="s">
+      <c r="J10" s="19" t="s">
         <v>2</v>
       </c>
       <c r="AA10" s="2"/>
@@ -1080,7 +1080,7 @@
       <c r="B11" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="51" t="s">
+      <c r="C11" s="21" t="s">
         <v>32</v>
       </c>
       <c r="D11" s="7" t="s">
@@ -1142,17 +1142,17 @@
       <c r="AA12" s="2"/>
     </row>
     <row r="13" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="43" t="s">
+      <c r="A13" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="43"/>
-      <c r="C13" s="43"/>
-      <c r="D13" s="43"/>
-      <c r="E13" s="43"/>
-      <c r="F13" s="43"/>
-      <c r="G13" s="43"/>
-      <c r="H13" s="43"/>
-      <c r="I13" s="43"/>
+      <c r="B13" s="44"/>
+      <c r="C13" s="44"/>
+      <c r="D13" s="44"/>
+      <c r="E13" s="44"/>
+      <c r="F13" s="44"/>
+      <c r="G13" s="44"/>
+      <c r="H13" s="44"/>
+      <c r="I13" s="44"/>
       <c r="J13" s="8">
         <f>SUM(J11:J12)</f>
         <v>400000</v>
@@ -1160,11 +1160,11 @@
       <c r="AA13" s="2"/>
     </row>
     <row r="14" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="44"/>
-      <c r="B14" s="44"/>
-      <c r="C14" s="44"/>
-      <c r="D14" s="44"/>
-      <c r="E14" s="44"/>
+      <c r="A14" s="45"/>
+      <c r="B14" s="45"/>
+      <c r="C14" s="45"/>
+      <c r="D14" s="45"/>
+      <c r="E14" s="45"/>
       <c r="F14" s="14"/>
       <c r="G14" s="14"/>
       <c r="H14" s="14"/>
@@ -1178,45 +1178,45 @@
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
       <c r="E15" s="5"/>
-      <c r="F15" s="21"/>
-      <c r="G15" s="21"/>
-      <c r="H15" s="21"/>
-      <c r="I15" s="21"/>
-      <c r="J15" s="21"/>
+      <c r="F15" s="22"/>
+      <c r="G15" s="22"/>
+      <c r="H15" s="22"/>
+      <c r="I15" s="22"/>
+      <c r="J15" s="22"/>
       <c r="AA15" s="2"/>
     </row>
     <row r="16" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="19" t="s">
+      <c r="A16" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="B16" s="19"/>
-      <c r="C16" s="19"/>
-      <c r="D16" s="19"/>
+      <c r="B16" s="50"/>
+      <c r="C16" s="50"/>
+      <c r="D16" s="50"/>
       <c r="E16" s="10"/>
-      <c r="F16" s="19" t="s">
+      <c r="F16" s="50" t="s">
         <v>19</v>
       </c>
-      <c r="G16" s="19"/>
-      <c r="H16" s="19"/>
-      <c r="I16" s="19"/>
-      <c r="J16" s="19"/>
+      <c r="G16" s="50"/>
+      <c r="H16" s="50"/>
+      <c r="I16" s="50"/>
+      <c r="J16" s="50"/>
       <c r="AA16" s="2"/>
     </row>
     <row r="17" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="20" t="s">
+      <c r="A17" s="51" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="20"/>
-      <c r="C17" s="20"/>
-      <c r="D17" s="20"/>
+      <c r="B17" s="51"/>
+      <c r="C17" s="51"/>
+      <c r="D17" s="51"/>
       <c r="E17" s="12"/>
-      <c r="F17" s="21" t="s">
+      <c r="F17" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="G17" s="21"/>
-      <c r="H17" s="21"/>
-      <c r="I17" s="21"/>
-      <c r="J17" s="21"/>
+      <c r="G17" s="22"/>
+      <c r="H17" s="22"/>
+      <c r="I17" s="22"/>
+      <c r="J17" s="22"/>
       <c r="AA17" s="2"/>
     </row>
     <row r="18" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -1287,20 +1287,20 @@
       <c r="AA22" s="2"/>
     </row>
     <row r="23" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="18" t="s">
+      <c r="A23" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="B23" s="18"/>
-      <c r="C23" s="18"/>
-      <c r="D23" s="18"/>
+      <c r="B23" s="49"/>
+      <c r="C23" s="49"/>
+      <c r="D23" s="49"/>
       <c r="E23" s="11"/>
-      <c r="F23" s="18" t="s">
+      <c r="F23" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="G23" s="18"/>
-      <c r="H23" s="18"/>
-      <c r="I23" s="18"/>
-      <c r="J23" s="18"/>
+      <c r="G23" s="49"/>
+      <c r="H23" s="49"/>
+      <c r="I23" s="49"/>
+      <c r="J23" s="49"/>
       <c r="AA23" s="2"/>
     </row>
     <row r="24" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -1377,6 +1377,12 @@
   </sheetData>
   <dataConsolidate/>
   <mergeCells count="19">
+    <mergeCell ref="F23:J23"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="F16:J16"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="F17:J17"/>
     <mergeCell ref="F15:J15"/>
     <mergeCell ref="A1:C4"/>
     <mergeCell ref="D2:J2"/>
@@ -1390,12 +1396,6 @@
     <mergeCell ref="A7:C7"/>
     <mergeCell ref="A14:E14"/>
     <mergeCell ref="A5:J5"/>
-    <mergeCell ref="F23:J23"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="F16:J16"/>
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="F17:J17"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="D4" r:id="rId1" display="http://vnetgps.vn" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
